--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N97_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N97_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.5972010965007</v>
+        <v>9.034545178181364</v>
       </c>
       <c r="D2" t="n">
-        <v>46.43725565012745</v>
+        <v>7.546054043145711</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80252549355199</v>
+        <v>1.917910392702199</v>
       </c>
       <c r="F2" t="n">
-        <v>11.42748182836467</v>
+        <v>1.85696579710926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.67114312837833</v>
+        <v>6.446560758361479</v>
       </c>
       <c r="D3" t="n">
-        <v>39.94494969563532</v>
+        <v>6.49105432554074</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80252549355199</v>
+        <v>1.917910392702199</v>
       </c>
       <c r="F3" t="n">
-        <v>11.42748182836467</v>
+        <v>1.85696579710926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.80887585429376</v>
+        <v>6.468942326322736</v>
       </c>
       <c r="D4" t="n">
-        <v>40.00586567459559</v>
+        <v>6.500953172121783</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80252549355199</v>
+        <v>1.917910392702199</v>
       </c>
       <c r="F4" t="n">
-        <v>11.42748182836467</v>
+        <v>1.85696579710926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.81624282080408</v>
+        <v>11.02013945838066</v>
       </c>
       <c r="D5" t="n">
-        <v>67.80711709316489</v>
+        <v>11.0186565276393</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80252549355199</v>
+        <v>1.917910392702199</v>
       </c>
       <c r="F5" t="n">
-        <v>11.42748182836467</v>
+        <v>1.85696579710926</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
